--- a/data/names.xlsx
+++ b/data/names.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\green\Documents\GitHub\tesi_tirabassi\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344A4F8F-B925-4E2A-9EA0-5D523362EE7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5624DF-2030-487E-94B6-E3F2D0903125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{87336021-60E8-411B-9B21-0E19CED005BF}"/>
+    <workbookView xWindow="0" yWindow="80" windowWidth="19200" windowHeight="11200" xr2:uid="{6DD82482-F4BD-4138-8E51-A819C0FD5B25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,9 +36,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="104">
-  <si>
-    <t>Network</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="142">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Brain Area</t>
+  </si>
+  <si>
+    <t>Abbreviation</t>
+  </si>
+  <si>
+    <t>Division</t>
+  </si>
+  <si>
+    <t>Primary motor area</t>
   </si>
   <si>
     <t>MOp_r</t>
@@ -47,178 +59,292 @@
     <t>LCN</t>
   </si>
   <si>
-    <t>Somatomotor</t>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>Cortical</t>
+  </si>
+  <si>
+    <t>Secondary motor area</t>
   </si>
   <si>
     <t>MOs_r</t>
   </si>
   <si>
-    <t>LCN/DMN</t>
-  </si>
-  <si>
-    <t>Prefrontal</t>
+    <t>PF</t>
+  </si>
+  <si>
+    <t>Primary somatosensory area</t>
   </si>
   <si>
     <t>SSp_r</t>
   </si>
   <si>
+    <t>Supplementary somatomotor area</t>
+  </si>
+  <si>
     <t>SSs_r</t>
   </si>
   <si>
+    <t>Gustatory areas</t>
+  </si>
+  <si>
     <t>GU_r</t>
   </si>
   <si>
-    <t>DMN postero-lateral</t>
-  </si>
-  <si>
-    <t>Anterolateral</t>
+    <t>DMNpostl</t>
+  </si>
+  <si>
+    <t>antL</t>
+  </si>
+  <si>
+    <t>Visual areas</t>
   </si>
   <si>
     <t>VIS_r</t>
   </si>
   <si>
-    <t>Visual network</t>
-  </si>
-  <si>
-    <t>Visual</t>
+    <t>VIS</t>
+  </si>
+  <si>
+    <t>Auditory areas</t>
   </si>
   <si>
     <t>AUD_r</t>
   </si>
   <si>
-    <t>Auditory network</t>
-  </si>
-  <si>
-    <t>Temporal</t>
+    <t>AUD</t>
+  </si>
+  <si>
+    <t>TEMP</t>
+  </si>
+  <si>
+    <t>Anterior cingulate area, dorsal part</t>
   </si>
   <si>
     <t>ACAd_r</t>
   </si>
   <si>
-    <t>DMN midline/SAL</t>
+    <t>Anterior cingulate area, ventral part</t>
   </si>
   <si>
     <t>ACAv_r</t>
   </si>
   <si>
-    <t>DMN midline</t>
+    <t>DMNmid</t>
+  </si>
+  <si>
+    <t>Prelimbic area</t>
   </si>
   <si>
     <t>PL_r</t>
   </si>
   <si>
+    <t>Infralimbic area</t>
+  </si>
+  <si>
     <t>ILA_r</t>
   </si>
   <si>
+    <t>Orbital area</t>
+  </si>
+  <si>
     <t>ORB_r</t>
   </si>
   <si>
+    <t>Agranular insular area, dorsal part</t>
+  </si>
+  <si>
     <t>AId_r</t>
   </si>
   <si>
     <t>SAL</t>
   </si>
   <si>
+    <t>Agranular insular area, posterior part</t>
+  </si>
+  <si>
     <t>AIp_r</t>
   </si>
   <si>
+    <t>Agranular insular area, ventral part</t>
+  </si>
+  <si>
     <t>AIv_r</t>
   </si>
   <si>
+    <t>Retrosplenial area, lateral agranular part</t>
+  </si>
+  <si>
     <t>RSPagl_r</t>
   </si>
   <si>
-    <t>Medial</t>
+    <t>MED</t>
+  </si>
+  <si>
+    <t>Retrosplenial area, dorsal part</t>
   </si>
   <si>
     <t>RSPd_r</t>
   </si>
   <si>
+    <t>Retrosplenial area, ventral part</t>
+  </si>
+  <si>
     <t>RSPv_r</t>
   </si>
   <si>
+    <t>Posterior parietal association areas</t>
+  </si>
+  <si>
     <t>PTLp_r</t>
   </si>
   <si>
+    <t>Temporal association areas</t>
+  </si>
+  <si>
     <t>TEa_r</t>
   </si>
   <si>
+    <t>Perirhinal area</t>
+  </si>
+  <si>
     <t>PERI_r</t>
   </si>
   <si>
-    <t>Hippocampus</t>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>Ectorhinal area</t>
   </si>
   <si>
     <t>ECT_r</t>
   </si>
   <si>
+    <t>Visceral area</t>
+  </si>
+  <si>
     <t>VISC_r</t>
   </si>
   <si>
+    <t>Piriform area</t>
+  </si>
+  <si>
     <t>PIR_r</t>
   </si>
   <si>
-    <t>Not assigned</t>
+    <t>not assigned</t>
+  </si>
+  <si>
+    <t>OLF</t>
+  </si>
+  <si>
+    <t>Ammon's horn</t>
   </si>
   <si>
     <t>CA_r</t>
   </si>
   <si>
+    <t>HPF</t>
+  </si>
+  <si>
+    <t>Dentate gyrus</t>
+  </si>
+  <si>
     <t>DG_r</t>
   </si>
   <si>
+    <t>Entorhinal area</t>
+  </si>
+  <si>
     <t>ENT_r</t>
   </si>
   <si>
+    <t>Subiculum</t>
+  </si>
+  <si>
     <t>SUB_r</t>
   </si>
   <si>
+    <t>Cortical subplate</t>
+  </si>
+  <si>
     <t>CTXsp_r</t>
   </si>
   <si>
+    <t>CTXsp</t>
+  </si>
+  <si>
+    <t>Striatum dorsal region</t>
+  </si>
+  <si>
     <t>STRd_r</t>
   </si>
   <si>
-    <t>DMN subcortical</t>
-  </si>
-  <si>
-    <t>Striatum</t>
+    <t>DMNsub</t>
+  </si>
+  <si>
+    <t>STR</t>
+  </si>
+  <si>
+    <t>Subcortical</t>
+  </si>
+  <si>
+    <t>Striatum ventral region</t>
   </si>
   <si>
     <t>STRv_r</t>
   </si>
   <si>
-    <t>LCN subcortical</t>
+    <t>LCNsub</t>
+  </si>
+  <si>
+    <t>Lateral septal complex</t>
   </si>
   <si>
     <t>LSX_r</t>
   </si>
   <si>
-    <t>BASAL FOREBRAIN</t>
-  </si>
-  <si>
     <t>Basal Forebrain</t>
   </si>
   <si>
-    <t>sAMY_r</t>
+    <t>Striatum-like amygdalar nuclei</t>
+  </si>
+  <si>
+    <t>SAMY_r</t>
+  </si>
+  <si>
+    <t>Pallidum</t>
   </si>
   <si>
     <t>PAL_r</t>
   </si>
   <si>
+    <t>PAL</t>
+  </si>
+  <si>
+    <t>Thalamus, sensory-motor cortex related</t>
+  </si>
+  <si>
     <t>DORsm_r</t>
   </si>
   <si>
-    <t>Thalamus</t>
+    <t>THAL</t>
+  </si>
+  <si>
+    <t>Thalamus, polymodal association cortex related</t>
   </si>
   <si>
     <t>DORpm_r</t>
   </si>
   <si>
+    <t>Hypothalamus</t>
+  </si>
+  <si>
     <t>HY_r</t>
   </si>
   <si>
-    <t>Hypothalamus</t>
+    <t>HY</t>
   </si>
   <si>
     <t>MOp_l</t>
@@ -317,7 +443,7 @@
     <t>LSX_l</t>
   </si>
   <si>
-    <t>sAMY_l</t>
+    <t>SAMY_l</t>
   </si>
   <si>
     <t>PAL_l</t>
@@ -332,22 +458,10 @@
     <t>HY_l</t>
   </si>
   <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>Macro</t>
-  </si>
-  <si>
-    <t>Node</t>
-  </si>
-  <si>
-    <t>Division</t>
-  </si>
-  <si>
-    <t>Cortical</t>
-  </si>
-  <si>
-    <t>Subcortical</t>
+    <t>Functional_Network</t>
+  </si>
+  <si>
+    <t>Macro_Area</t>
   </si>
 </sst>
 </file>
@@ -718,1230 +832,1457 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DAC94AE-C54F-42A3-95CB-83015938355B}">
-  <dimension ref="A1:E75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED02C2B9-6AE4-45A1-9883-A0C6B53E09DA}">
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" customWidth="1"/>
-    <col min="2" max="2" width="17.81640625" customWidth="1"/>
-    <col min="3" max="3" width="20.54296875" customWidth="1"/>
-    <col min="4" max="4" width="19.54296875" customWidth="1"/>
-    <col min="5" max="5" width="15.1796875" customWidth="1"/>
+    <col min="2" max="2" width="39.81640625" customWidth="1"/>
+    <col min="3" max="3" width="13.7265625" customWidth="1"/>
+    <col min="4" max="4" width="19.453125" customWidth="1"/>
+    <col min="5" max="5" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="E1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E13" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E14" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E16" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+      <c r="F17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" t="s">
         <v>31</v>
       </c>
-      <c r="C18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" t="s">
-        <v>30</v>
-      </c>
       <c r="E18" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+      <c r="F18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+      <c r="F19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+      <c r="F20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E21" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+      <c r="F21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="E22" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+      <c r="F22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="E23" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+      <c r="F23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>64</v>
+      </c>
+      <c r="D25" t="s">
+        <v>65</v>
       </c>
       <c r="E25" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+      <c r="F25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="E26" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="F26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="D27" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="E27" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="F27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="E28" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="F28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="E29" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="F29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>40</v>
+        <v>77</v>
+      </c>
+      <c r="D30" t="s">
+        <v>65</v>
       </c>
       <c r="E30" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="F30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="D31" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="E31" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="F31" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="E32" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="F32" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="D33" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="E33" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="F33" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="C34" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="D34" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="E34" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="F34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="C35" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="D35" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="E35" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+      <c r="F35" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="D36" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="E36" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+      <c r="F36" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="C37" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="D37" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="E37" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+      <c r="F37" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="E38" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+      <c r="F38" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="D39" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E39" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="F39" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="C40" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
       <c r="D40" t="s">
         <v>6</v>
       </c>
       <c r="E40" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="F40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="D41" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E41" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="F41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>2</v>
+        <v>106</v>
       </c>
       <c r="D42" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E42" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="F42" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="D43" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E43" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="F43" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="D44" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E44" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="F44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="D45" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E45" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+      <c r="F45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="D46" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E46" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="F46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="C47" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="D47" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E47" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="F47" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C48" t="s">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="D48" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E48" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="F48" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="C49" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="D49" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E49" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="F49" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="C50" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="D50" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E50" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="F50" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="C51" t="s">
-        <v>26</v>
+        <v>115</v>
       </c>
       <c r="D51" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E51" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="F51" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="C52" t="s">
-        <v>26</v>
+        <v>116</v>
       </c>
       <c r="D52" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E52" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="F52" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="C53" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="D53" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E53" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="F53" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="C54" t="s">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="D54" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E54" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+      <c r="F54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="C55" t="s">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="D55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E55" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+      <c r="F55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="C56" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="D56" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E56" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+      <c r="F56" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="C57" t="s">
-        <v>10</v>
+        <v>121</v>
       </c>
       <c r="D57" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E57" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+      <c r="F57" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="C58" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D58" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E58" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+      <c r="F58" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="C59" t="s">
-        <v>36</v>
+        <v>123</v>
       </c>
       <c r="D59" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="E59" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+      <c r="F59" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="C60" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="D60" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="E60" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+      <c r="F60" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C61" t="s">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="D61" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E61" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+      <c r="F61" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C62" t="s">
-        <v>40</v>
+        <v>126</v>
+      </c>
+      <c r="D62" t="s">
+        <v>65</v>
       </c>
       <c r="E62" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+      <c r="F62" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>36</v>
+        <v>127</v>
       </c>
       <c r="D63" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="E63" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="F63" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="C64" t="s">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="D64" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="E64" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="F64" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="C65" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="D65" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="E65" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="F65" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C66" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="D66" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="E66" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+      <c r="F66" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C67" t="s">
-        <v>40</v>
+        <v>131</v>
+      </c>
+      <c r="D67" t="s">
+        <v>65</v>
       </c>
       <c r="E67" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="F67" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="D68" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="E68" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="F68" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C69" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="D69" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="E69" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="F69" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C70" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="D70" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="E70" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="F70" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C71" t="s">
-        <v>52</v>
+        <v>135</v>
       </c>
       <c r="D71" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="E71" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="F71" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>92</v>
+      </c>
+      <c r="C72" t="s">
+        <v>136</v>
+      </c>
+      <c r="D72" t="s">
+        <v>89</v>
+      </c>
+      <c r="E72" t="s">
         <v>94</v>
       </c>
-      <c r="C72" t="s">
-        <v>52</v>
-      </c>
-      <c r="D72" t="s">
-        <v>53</v>
-      </c>
-      <c r="E72" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F72" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1949,50 +2290,60 @@
         <v>95</v>
       </c>
       <c r="C73" t="s">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="D73" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="E73" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+      <c r="F73" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C74" t="s">
-        <v>57</v>
+        <v>138</v>
       </c>
       <c r="D74" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="E74" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+      <c r="F74" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C75" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="D75" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="E75" t="s">
-        <v>103</v>
+        <v>102</v>
+      </c>
+      <c r="F75" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/names.xlsx
+++ b/data/names.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\green\Documents\GitHub\tesi_tirabassi\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5624DF-2030-487E-94B6-E3F2D0903125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA09436-577F-464C-9933-3A45F7635082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="80" windowWidth="19200" windowHeight="11200" xr2:uid="{6DD82482-F4BD-4138-8E51-A819C0FD5B25}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="100">
   <si>
     <t>ID</t>
   </si>
@@ -53,9 +53,6 @@
     <t>Primary motor area</t>
   </si>
   <si>
-    <t>MOp_r</t>
-  </si>
-  <si>
     <t>LCN</t>
   </si>
   <si>
@@ -68,30 +65,18 @@
     <t>Secondary motor area</t>
   </si>
   <si>
-    <t>MOs_r</t>
-  </si>
-  <si>
     <t>PF</t>
   </si>
   <si>
     <t>Primary somatosensory area</t>
   </si>
   <si>
-    <t>SSp_r</t>
-  </si>
-  <si>
     <t>Supplementary somatomotor area</t>
   </si>
   <si>
-    <t>SSs_r</t>
-  </si>
-  <si>
     <t>Gustatory areas</t>
   </si>
   <si>
-    <t>GU_r</t>
-  </si>
-  <si>
     <t>DMNpostl</t>
   </si>
   <si>
@@ -101,18 +86,12 @@
     <t>Visual areas</t>
   </si>
   <si>
-    <t>VIS_r</t>
-  </si>
-  <si>
     <t>VIS</t>
   </si>
   <si>
     <t>Auditory areas</t>
   </si>
   <si>
-    <t>AUD_r</t>
-  </si>
-  <si>
     <t>AUD</t>
   </si>
   <si>
@@ -122,117 +101,66 @@
     <t>Anterior cingulate area, dorsal part</t>
   </si>
   <si>
-    <t>ACAd_r</t>
-  </si>
-  <si>
     <t>Anterior cingulate area, ventral part</t>
   </si>
   <si>
-    <t>ACAv_r</t>
-  </si>
-  <si>
     <t>DMNmid</t>
   </si>
   <si>
     <t>Prelimbic area</t>
   </si>
   <si>
-    <t>PL_r</t>
-  </si>
-  <si>
     <t>Infralimbic area</t>
   </si>
   <si>
-    <t>ILA_r</t>
-  </si>
-  <si>
     <t>Orbital area</t>
   </si>
   <si>
-    <t>ORB_r</t>
-  </si>
-  <si>
     <t>Agranular insular area, dorsal part</t>
   </si>
   <si>
-    <t>AId_r</t>
-  </si>
-  <si>
     <t>SAL</t>
   </si>
   <si>
     <t>Agranular insular area, posterior part</t>
   </si>
   <si>
-    <t>AIp_r</t>
-  </si>
-  <si>
     <t>Agranular insular area, ventral part</t>
   </si>
   <si>
-    <t>AIv_r</t>
-  </si>
-  <si>
     <t>Retrosplenial area, lateral agranular part</t>
   </si>
   <si>
-    <t>RSPagl_r</t>
-  </si>
-  <si>
     <t>MED</t>
   </si>
   <si>
     <t>Retrosplenial area, dorsal part</t>
   </si>
   <si>
-    <t>RSPd_r</t>
-  </si>
-  <si>
     <t>Retrosplenial area, ventral part</t>
   </si>
   <si>
-    <t>RSPv_r</t>
-  </si>
-  <si>
     <t>Posterior parietal association areas</t>
   </si>
   <si>
-    <t>PTLp_r</t>
-  </si>
-  <si>
     <t>Temporal association areas</t>
   </si>
   <si>
-    <t>TEa_r</t>
-  </si>
-  <si>
     <t>Perirhinal area</t>
   </si>
   <si>
-    <t>PERI_r</t>
-  </si>
-  <si>
     <t>HP</t>
   </si>
   <si>
     <t>Ectorhinal area</t>
   </si>
   <si>
-    <t>ECT_r</t>
-  </si>
-  <si>
     <t>Visceral area</t>
   </si>
   <si>
-    <t>VISC_r</t>
-  </si>
-  <si>
     <t>Piriform area</t>
   </si>
   <si>
-    <t>PIR_r</t>
-  </si>
-  <si>
     <t>not assigned</t>
   </si>
   <si>
@@ -242,45 +170,27 @@
     <t>Ammon's horn</t>
   </si>
   <si>
-    <t>CA_r</t>
-  </si>
-  <si>
     <t>HPF</t>
   </si>
   <si>
     <t>Dentate gyrus</t>
   </si>
   <si>
-    <t>DG_r</t>
-  </si>
-  <si>
     <t>Entorhinal area</t>
   </si>
   <si>
-    <t>ENT_r</t>
-  </si>
-  <si>
     <t>Subiculum</t>
   </si>
   <si>
-    <t>SUB_r</t>
-  </si>
-  <si>
     <t>Cortical subplate</t>
   </si>
   <si>
-    <t>CTXsp_r</t>
-  </si>
-  <si>
     <t>CTXsp</t>
   </si>
   <si>
     <t>Striatum dorsal region</t>
   </si>
   <si>
-    <t>STRd_r</t>
-  </si>
-  <si>
     <t>DMNsub</t>
   </si>
   <si>
@@ -293,175 +203,139 @@
     <t>Striatum ventral region</t>
   </si>
   <si>
-    <t>STRv_r</t>
-  </si>
-  <si>
     <t>LCNsub</t>
   </si>
   <si>
     <t>Lateral septal complex</t>
   </si>
   <si>
-    <t>LSX_r</t>
-  </si>
-  <si>
     <t>Basal Forebrain</t>
   </si>
   <si>
     <t>Striatum-like amygdalar nuclei</t>
   </si>
   <si>
-    <t>SAMY_r</t>
-  </si>
-  <si>
     <t>Pallidum</t>
   </si>
   <si>
-    <t>PAL_r</t>
-  </si>
-  <si>
     <t>PAL</t>
   </si>
   <si>
     <t>Thalamus, sensory-motor cortex related</t>
   </si>
   <si>
-    <t>DORsm_r</t>
-  </si>
-  <si>
     <t>THAL</t>
   </si>
   <si>
     <t>Thalamus, polymodal association cortex related</t>
   </si>
   <si>
-    <t>DORpm_r</t>
-  </si>
-  <si>
     <t>Hypothalamus</t>
   </si>
   <si>
-    <t>HY_r</t>
-  </si>
-  <si>
     <t>HY</t>
   </si>
   <si>
-    <t>MOp_l</t>
-  </si>
-  <si>
-    <t>MOs_l</t>
-  </si>
-  <si>
-    <t>SSp_l</t>
-  </si>
-  <si>
-    <t>SSs_l</t>
-  </si>
-  <si>
-    <t>GU_l</t>
-  </si>
-  <si>
-    <t>VIS_l</t>
-  </si>
-  <si>
-    <t>AUD_l</t>
-  </si>
-  <si>
-    <t>ACAd_l</t>
-  </si>
-  <si>
-    <t>ACAv_l</t>
-  </si>
-  <si>
-    <t>PL_l</t>
-  </si>
-  <si>
-    <t>ILA_l</t>
-  </si>
-  <si>
-    <t>ORB_l</t>
-  </si>
-  <si>
-    <t>AId_l</t>
-  </si>
-  <si>
-    <t>AIp_l</t>
-  </si>
-  <si>
-    <t>AIv_l</t>
-  </si>
-  <si>
-    <t>RSPagl_l</t>
-  </si>
-  <si>
-    <t>RSPd_l</t>
-  </si>
-  <si>
-    <t>RSPv_l</t>
-  </si>
-  <si>
-    <t>PTLp_l</t>
-  </si>
-  <si>
-    <t>TEa_l</t>
-  </si>
-  <si>
-    <t>PERI_l</t>
-  </si>
-  <si>
-    <t>ECT_l</t>
-  </si>
-  <si>
-    <t>VISC_l</t>
-  </si>
-  <si>
-    <t>PIR_l</t>
-  </si>
-  <si>
-    <t>CA_l</t>
-  </si>
-  <si>
-    <t>DG_l</t>
-  </si>
-  <si>
-    <t>ENT_l</t>
-  </si>
-  <si>
-    <t>SUB_l</t>
-  </si>
-  <si>
-    <t>CTXsp_l</t>
-  </si>
-  <si>
-    <t>STRd_l</t>
-  </si>
-  <si>
-    <t>STRv_l</t>
-  </si>
-  <si>
-    <t>LSX_l</t>
-  </si>
-  <si>
-    <t>SAMY_l</t>
-  </si>
-  <si>
-    <t>PAL_l</t>
-  </si>
-  <si>
-    <t>DORsm_l</t>
-  </si>
-  <si>
-    <t>DORpm_l</t>
-  </si>
-  <si>
-    <t>HY_l</t>
-  </si>
-  <si>
     <t>Functional_Network</t>
   </si>
   <si>
     <t>Macro_Area</t>
+  </si>
+  <si>
+    <t>DG</t>
+  </si>
+  <si>
+    <t>ENT</t>
+  </si>
+  <si>
+    <t>SUB</t>
+  </si>
+  <si>
+    <t>STRd</t>
+  </si>
+  <si>
+    <t>STRv</t>
+  </si>
+  <si>
+    <t>LSX</t>
+  </si>
+  <si>
+    <t>SAMY</t>
+  </si>
+  <si>
+    <t>DORsm</t>
+  </si>
+  <si>
+    <t>DORpm</t>
+  </si>
+  <si>
+    <t>Mop</t>
+  </si>
+  <si>
+    <t>Mos</t>
+  </si>
+  <si>
+    <t>SSp</t>
+  </si>
+  <si>
+    <t>SSs</t>
+  </si>
+  <si>
+    <t>GU</t>
+  </si>
+  <si>
+    <t>ACAd</t>
+  </si>
+  <si>
+    <t>ACAv</t>
+  </si>
+  <si>
+    <t>PL</t>
+  </si>
+  <si>
+    <t>ILA</t>
+  </si>
+  <si>
+    <t>ORB</t>
+  </si>
+  <si>
+    <t>Aid</t>
+  </si>
+  <si>
+    <t>Aip</t>
+  </si>
+  <si>
+    <t>Aiv</t>
+  </si>
+  <si>
+    <t>RSPagl</t>
+  </si>
+  <si>
+    <t>RSPd</t>
+  </si>
+  <si>
+    <t>RSPv</t>
+  </si>
+  <si>
+    <t>PTLp</t>
+  </si>
+  <si>
+    <t>Tea</t>
+  </si>
+  <si>
+    <t>PERI</t>
+  </si>
+  <si>
+    <t>ECT</t>
+  </si>
+  <si>
+    <t>VISC</t>
+  </si>
+  <si>
+    <t>PIR</t>
+  </si>
+  <si>
+    <t>CA</t>
   </si>
 </sst>
 </file>
@@ -839,7 +713,8 @@
     <col min="2" max="2" width="39.81640625" customWidth="1"/>
     <col min="3" max="3" width="13.7265625" customWidth="1"/>
     <col min="4" max="4" width="19.453125" customWidth="1"/>
-    <col min="5" max="5" width="12.54296875" customWidth="1"/>
+    <col min="5" max="5" width="24.1796875" customWidth="1"/>
+    <col min="6" max="6" width="17.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -853,10 +728,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>140</v>
+        <v>66</v>
       </c>
       <c r="E1" t="s">
-        <v>141</v>
+        <v>67</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -870,16 +745,16 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -887,19 +762,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
       <c r="F3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -907,19 +782,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
         <v>6</v>
       </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
       <c r="F4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -927,19 +802,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
         <v>6</v>
       </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
       <c r="F5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -947,19 +822,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -967,19 +842,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -987,19 +862,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -1007,19 +882,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -1027,19 +902,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -1047,19 +922,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -1067,19 +942,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -1087,19 +962,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -1107,19 +982,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -1127,19 +1002,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -1147,19 +1022,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -1167,19 +1042,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" t="s">
         <v>31</v>
       </c>
-      <c r="E17" t="s">
-        <v>47</v>
-      </c>
       <c r="F17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -1187,19 +1062,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" t="s">
         <v>31</v>
       </c>
-      <c r="E18" t="s">
-        <v>47</v>
-      </c>
       <c r="F18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -1207,19 +1082,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" t="s">
         <v>31</v>
       </c>
-      <c r="E19" t="s">
-        <v>47</v>
-      </c>
       <c r="F19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -1227,19 +1102,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="F20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -1247,19 +1122,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E21" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -1267,19 +1142,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E22" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -1287,19 +1162,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E23" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -1307,19 +1182,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -1327,19 +1202,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="E25" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="F25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -1347,19 +1222,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E26" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="F26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -1367,19 +1242,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E27" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="F27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -1387,19 +1262,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E28" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="F28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -1407,19 +1282,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E29" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="F29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -1427,19 +1302,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="E30" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="F30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -1447,19 +1322,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D31" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="E31" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="F31" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -1467,19 +1342,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D32" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="E32" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="F32" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -1487,19 +1362,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D33" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="E33" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="F33" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -1507,19 +1382,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="C34" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="E34" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="F34" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -1527,19 +1402,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="C35" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="D35" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="E35" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="F35" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -1547,19 +1422,19 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D36" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="E36" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="F36" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -1567,19 +1442,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="C37" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="D37" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="E37" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="F37" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -1587,19 +1462,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="C38" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="D38" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="E38" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="F38" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -1610,16 +1485,16 @@
         <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="D39" t="s">
+        <v>5</v>
+      </c>
+      <c r="E39" t="s">
         <v>6</v>
       </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
       <c r="F39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -1627,19 +1502,19 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" t="s">
+        <v>78</v>
+      </c>
+      <c r="D40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E40" t="s">
         <v>9</v>
       </c>
-      <c r="C40" t="s">
-        <v>104</v>
-      </c>
-      <c r="D40" t="s">
-        <v>6</v>
-      </c>
-      <c r="E40" t="s">
-        <v>11</v>
-      </c>
       <c r="F40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -1647,19 +1522,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="D41" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" t="s">
         <v>6</v>
       </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
       <c r="F41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -1667,19 +1542,19 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C42" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="D42" t="s">
+        <v>5</v>
+      </c>
+      <c r="E42" t="s">
         <v>6</v>
       </c>
-      <c r="E42" t="s">
-        <v>7</v>
-      </c>
       <c r="F42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -1687,19 +1562,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="D43" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -1707,19 +1582,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C44" t="s">
-        <v>108</v>
+        <v>16</v>
       </c>
       <c r="D44" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E44" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F44" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -1727,19 +1602,19 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -1747,19 +1622,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C46" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="D46" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -1767,19 +1642,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C47" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="D47" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -1787,19 +1662,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C48" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="D48" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E48" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
@@ -1807,19 +1682,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C49" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="D49" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E49" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F49" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
@@ -1827,19 +1702,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C50" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="D50" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E50" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
@@ -1847,19 +1722,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="D51" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E51" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F51" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
@@ -1867,19 +1742,19 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="D52" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E52" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
@@ -1887,19 +1762,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C53" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="D53" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E53" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F53" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
@@ -1907,19 +1782,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C54" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="D54" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" t="s">
         <v>31</v>
       </c>
-      <c r="E54" t="s">
-        <v>47</v>
-      </c>
       <c r="F54" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
@@ -1927,19 +1802,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C55" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="D55" t="s">
+        <v>22</v>
+      </c>
+      <c r="E55" t="s">
         <v>31</v>
       </c>
-      <c r="E55" t="s">
-        <v>47</v>
-      </c>
       <c r="F55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
@@ -1947,19 +1822,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C56" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="D56" t="s">
+        <v>22</v>
+      </c>
+      <c r="E56" t="s">
         <v>31</v>
       </c>
-      <c r="E56" t="s">
-        <v>47</v>
-      </c>
       <c r="F56" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
@@ -1967,19 +1842,19 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C57" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="D57" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E57" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="F57" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
@@ -1987,19 +1862,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="C58" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="D58" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E58" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -2007,19 +1882,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="C59" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="D59" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E59" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F59" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
@@ -2027,19 +1902,19 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="C60" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="D60" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E60" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F60" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
@@ -2047,19 +1922,19 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C61" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="D61" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E61" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F61" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
@@ -2067,19 +1942,19 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="C62" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="D62" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="E62" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="F62" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
@@ -2087,19 +1962,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="C63" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="D63" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E63" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="F63" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
@@ -2107,19 +1982,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C64" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="D64" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E64" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="F64" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
@@ -2127,19 +2002,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="C65" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="D65" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E65" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="F65" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -2147,19 +2022,19 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="C66" t="s">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="D66" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E66" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="F66" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -2167,19 +2042,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="C67" t="s">
-        <v>131</v>
+        <v>49</v>
       </c>
       <c r="D67" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="E67" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="F67" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
@@ -2187,19 +2062,19 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="C68" t="s">
-        <v>132</v>
+        <v>71</v>
       </c>
       <c r="D68" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="E68" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="F68" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -2207,19 +2082,19 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="C69" t="s">
-        <v>133</v>
+        <v>72</v>
       </c>
       <c r="D69" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="E69" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="F69" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -2227,19 +2102,19 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="C70" t="s">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="D70" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="E70" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="F70" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
@@ -2247,19 +2122,19 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="C71" t="s">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="D71" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="E71" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="F71" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
@@ -2267,19 +2142,19 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="C72" t="s">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="D72" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="E72" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="F72" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
@@ -2287,19 +2162,19 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="C73" t="s">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="D73" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="E73" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="F73" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
@@ -2307,19 +2182,19 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="C74" t="s">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="D74" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="E74" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="F74" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
@@ -2327,19 +2202,19 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="C75" t="s">
-        <v>139</v>
+        <v>65</v>
       </c>
       <c r="D75" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="E75" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="F75" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
